--- a/evidencias/Lista_Chequeo_Cuarto_Avance_REACT_FASTAPI_DILIGENCIADA.xlsx
+++ b/evidencias/Lista_Chequeo_Cuarto_Avance_REACT_FASTAPI_DILIGENCIADA.xlsx
@@ -493,7 +493,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -881,17 +881,297 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4953000" cy="2219325"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3371850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="2562225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="2276475"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3095625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2943225" cy="4000500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -915,11 +1195,11 @@
     <ext cx="4953000" cy="3095625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
+        <a:blip cstate="print" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -937,306 +1217,23 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3371850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="2562225"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="2276475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4953000" cy="3095625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2943225" cy="4000500"/>
+    <ext cx="4953000" cy="2390775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
+        <a:blip cstate="print" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2131,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="185" customHeight="1" s="28">
+    <row r="27" ht="198" customHeight="1" s="28">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>REQ-14</t>
@@ -2155,7 +2152,7 @@
       <c r="E27" s="41" t="n"/>
       <c r="F27" s="42" t="inlineStr">
         <is>
-          <t>21 endpoints REST agrupados por entidad: /api/auth, /api/usuarios, /api/productos y /api/servicios, más las rutas de sistema / y /salud. Todos documentados automáticamente en Swagger.</t>
+          <t>24 endpoints REST agrupados por entidad: /api/auth (incluida la recuperación de contraseña), /api/usuarios, /api/productos y /api/servicios, más las rutas de sistema / y /salud. Todos documentados automáticamente en Swagger.</t>
         </is>
       </c>
     </row>
@@ -2175,15 +2172,15 @@
           <t>implementacion de la funcionalidad de  recuperación de contraseña olvidada por el usuario (Cliente-Empleado)</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>En Desarrollo</t>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E28" s="41" t="n"/>
       <c r="F28" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE POR COMPLETAR. El formulario existe en el Frontend (components/RecoverPassword.jsx) y valida el correo electrónico, pero aún no hay un endpoint en FastAPI que genere el token de restablecimiento ni el envío del correo. Es el único requerimiento que falta.</t>
+          <t>Flujo completo implementado. POST /api/auth/recuperar-password genera un enlace de un solo uso con vigencia de 30 minutos; GET /api/auth/restablecer-password/{token} lo verifica antes de mostrar el formulario y POST /api/auth/restablecer-password guarda la nueva contraseña como hash bcrypt. En la tabla tokens_recuperacion solo se almacena el hash SHA-256 del token, nunca el token en claro. La respuesta es idéntica exista o no el correo, para no revelar qué direcciones están registradas. Sin servidor de correo configurado, el enlace se registra en la consola del Backend (app/core/notificaciones.py). Cubierto por 14 pruebas automáticas en tests/test_recuperacion.py.</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2460,7 @@
       <c r="E38" s="41" t="n"/>
       <c r="F38" s="42" t="inlineStr">
         <is>
-          <t>Swagger UI activo en http://127.0.0.1:8000/docs con los 21 endpoints, sus esquemas de entrada y salida, y el botón Authorize para probar los endpoints protegidos con el JWT.</t>
+          <t>Swagger UI activo en http://127.0.0.1:8000/docs con los 24 endpoints, sus esquemas de entrada y salida, y el botón Authorize para probar los endpoints protegidos con el JWT.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2488,7 @@
       <c r="E39" s="41" t="n"/>
       <c r="F39" s="42" t="inlineStr">
         <is>
-          <t>Colección de Postman en backend/postman/ con 33 peticiones organizadas en seis carpetas. Se evidencian GET, POST, PUT, PATCH y DELETE con respuestas correctas y de error. Además, 40 pruebas automáticas con pytest.</t>
+          <t>Colección de Postman en backend/postman/ con 33 peticiones organizadas en seis carpetas. Se evidencian GET, POST, PUT, PATCH y DELETE con respuestas correctas y de error. Además, 54 pruebas automáticas con pytest.</t>
         </is>
       </c>
     </row>
